--- a/fixed_trading_intraday_intraday.xlsx
+++ b/fixed_trading_intraday_intraday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,1026 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-09-09T19:13:38</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.1913</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.1497</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.0215</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-09-09T19:26:51</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0229</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-09-09T19:40:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.0246</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-09-09T19:53:14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.2411</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.2429</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-09-09T20:06:47</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.0068</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.1493</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-09-09T20:20:14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-09T20:33:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.5759</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09-09T20:47:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.2676</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-09-09T21:00:56</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.1037</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-09-09T21:14:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-09-09T21:28:13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.191</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1552</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-09-09T21:41:41</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2107</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-09-09T21:55:05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:09:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.8182</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.1978</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:18:05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:24:44</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.4255</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.2691</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:31:21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.9719</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2571</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:37:58</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:44:39</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>trial_018</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.6538</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 330}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-09T22:51:11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>trial_019</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.1234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.0244</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.0198</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 3.950916564838231e-05, "batch_size": 1024, "gamma": 0.9646752384611725, "net_dimension": 512, "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 331}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixed_trading_intraday_intraday.xlsx
+++ b/fixed_trading_intraday_intraday.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,6 +1566,2658 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:30:06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.8783</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.3814</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.0332</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:31:12</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.6774</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.3651</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:31:38</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.7778</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.3901</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.0228</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:39:31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-3.4694</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.5311</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:41:08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-6.2355</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.6066</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.0356</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:48:04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.9298</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.4399</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1916</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.0406</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:50:27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.7027</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:56:24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-2.7609</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.3713</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-11T13:59:18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-4.036</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.4812</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:04:25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-3.3617</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.4537</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.0391</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:07:45</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.3615</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.1627</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.0003</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:14:58</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.2839</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:22:06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-3.6928</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.4091</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:29:18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-4.4261</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.5056</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.0326</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:36:28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.7227</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:42:16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.0319</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:45:14</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-2.6697</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.2782</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1194</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:50:17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2.1614</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.3264</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:53:54</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-5.6013</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.6038</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.0209</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09-11T14:57:54</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-3.3513</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.4681</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:02:15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-2.8808</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.2816</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1126</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:05:41</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-5.867</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.598</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.0395</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:10:34</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4.0515</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:13:36</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-4.3163</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.5052</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:18:39</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-3.6532</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.3655</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:21:38</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.0184</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-3.793</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.4882</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.0139</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:26:53</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.4036</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1553</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:29:47</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-3.8043</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.4893</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.0387</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:35:23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>trial_015</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-4.6506</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.5001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 327}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:38:05</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-4.537</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.5508999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:43:55</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>trial_016</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.1902</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 328}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:46:25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-3.3945</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:52:34</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>trial_017</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.0197</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-6.1078</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-0.5113</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.0283</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 329}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-09-11T15:54:54</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-4.061</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-0.4995</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:01:23</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>trial_018</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-3.5208</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.3598</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 330}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:03:31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0.4163</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.0311</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:10:30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>trial_019</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.0483</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 331}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:12:18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-1.8707</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.2769</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:19:16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-2.9264</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.4113</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:28:11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-4.9511</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.5582</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:29:56</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-0.1637</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:36:25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FIXED_sac_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-2.8589</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.4065</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.0401</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:39:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.3785</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:49:11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-1.1095</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-0.1436</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.0214</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-09-11T16:58:27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-0.5106000000000001</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-0.0736</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.0166</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:07:45</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.4713</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.7157</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:17:34</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-2.6026</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-0.2596</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.0217</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:27:32</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-3.372</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-0.4181</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:36:51</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-1.0579</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.1894</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:46:38</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.0046</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.2999</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-0.1518</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.0592</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-09-11T17:57:09</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-3.7694</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.447</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-09-11T18:07:38</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FIXED_td3_trading_intraday_intraday_runs_batch</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-2.4767</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-0.3098</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.1454</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 1024, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 3.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "trading", "freq": "intraday", "dataset": "intraday"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
